--- a/09_plan_calidad/Diagramas/LafroX-Calculos-SD9.xlsx
+++ b/09_plan_calidad/Diagramas/LafroX-Calculos-SD9.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -269,6 +269,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1566,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1747,6 +1750,28 @@
       </c>
       <c r="C14" s="42">
         <f>C9/Datos_Base!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Costo de conformidad / HH del proyecto</t>
+        </is>
+      </c>
+      <c r="C15" s="42">
+        <f>C11/Datos_Base!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Comprobación: prevención 4.224, evaluación 6.624, conformidad 10.848 HH (SD9 §9.1.5)</t>
+        </is>
+      </c>
+      <c r="C16" s="4">
+        <f>IF(AND(C5=4224,C6=6624,C11=10848),"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
@@ -4328,25 +4353,25 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Horas por día hábil</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="n">
-        <v>8</v>
+          <t>HH efectivas por persona y día hábil (8 h al 80 %)</t>
+        </is>
+      </c>
+      <c r="C51" s="48" t="n">
+        <v>6.4</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>HH/día</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Supuesto de cálculo (T-15 usa jornada de 8 h)</t>
+          <t>T-15 §4.1 y §5.1 (8 h al 80 %); SD9 §9.3.2</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Supuesto</t>
+          <t>Fuente</t>
         </is>
       </c>
     </row>
@@ -4851,17 +4876,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>p95 registro de entrega en el local</t>
+          <t>p95 registro de entrega en el local / otra transacción crítica de terreno, de extremo a extremo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>≤ 2 s</t>
+          <t>≤ 2 s / ≤ 3 s</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Caso cap. 15 RT-09.01</t>
+          <t>Caso cap. 15 RT-09.01; BTT §9.1; SD4 Tabla 31</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4893,17 +4918,17 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>p95 línea de preventa / consulta de stock y crédito</t>
+          <t>p95 línea de preventa / consulta de stock y crédito / búsqueda con criterios compuestos (búsqueda global de RF-17.11) / informe estándar en línea</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>≤ 1,5 s / ≤ 2 s</t>
+          <t>≤ 1,5 s / ≤ 2 s / ≤ 3 s (≤ 2 s) / ≤ 30 s</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Caso cap. 15 RT-09.01</t>
+          <t>Caso cap. 15 RT-09.01; BTT §9.1; SD3 Anexo 3.A, RF-17.11; SD4 Tabla 31</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -4918,7 +4943,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>3.8.4</t>
+          <t>3.8.4, 3.9.3</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4960,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>p95 API consulta / escritura / carga de página</t>
+          <t>p95 API consulta / escritura / carga de página / navegación entre vistas ya cargadas</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>≤ 500 ms / ≤ 800 ms / ≤ 2 s</t>
+          <t>≤ 500 ms / ≤ 800 ms / ≤ 2 s / ≤ 1 s</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4950,7 +4975,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Prueba de carga + regresión de desempeño semanal</t>
+          <t>Prueba de carga con medición en el navegador + regresión de desempeño semanal</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -5239,7 +5264,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BTT RT-13.01</t>
+          <t>BTT RT-13.01; W3C (2023)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5439,22 +5464,22 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Sincronización tras reconexión</t>
+          <t>Sincronización tras reconexión y resolución de conflictos de stock del CD</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Dispositivo ≤ 10 min; CD ≤ 2 h</t>
+          <t>Dispositivo ≤ 10 min; CD ≤ 2 h; 100 % de los conflictos de stock resueltos con la regla del SD4, Anexo 4-K, Tabla A.12, con el mismo resultado al repetir la reconciliación</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Caso RT-03.13</t>
+          <t>Caso RT-03.13; BTT RT-03.12; SD4 Anexo 4-K</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Prueba de desconexión controlada</t>
+          <t>Prueba de desconexión controlada con reservas concurrentes del mismo stock, reconciliadas dos veces sobre los mismos eventos y comparadas con su bitácora</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -5523,12 +5548,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Datos productivos fuera de Producción</t>
+          <t>Datos productivos en ambientes no productivos de prueba</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>0 registros</t>
+          <t>0 registros sin anonimización verificada; DR se trata como réplica productiva restringida</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -5538,7 +5563,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Escaneo Macie de QA y PREPROD</t>
+          <t>Escaneo Macie de QA y PREPROD y prueba de reidentificación</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -7673,7 +7698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7850,7 +7875,7 @@
         <v/>
       </c>
       <c r="C10" s="28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="22">
         <f>B10*C10</f>
@@ -7858,7 +7883,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Supuesto: éxito, error, lentitud, duplicado, orden, versión (RT-10.08)</t>
+          <t>Supuesto: éxito, dependencia que no responde, respuesta con error, respuesta con lentitud, duplicado, orden y versión (RT-10.08)</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7934,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Minutos por caso automatizado (paralelismo incluido)</t>
+          <t>Minutos por caso automatizado (un ejecutor)</t>
         </is>
       </c>
       <c r="C16" s="31" t="n">
@@ -8029,6 +8054,17 @@
       </c>
       <c r="D25" s="3">
         <f>IF(D22&lt;=8,"Sí","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Comprobación: total = 1.297 casos, 1.038 automatizados y 259 manuales (SD9 §9.2.3; Anexo 9.C.1)</t>
+        </is>
+      </c>
+      <c r="D26" s="3">
+        <f>IF(AND(D11=1297,D20=1038,D23=259),"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
@@ -8043,7 +8079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL57"/>
+  <dimension ref="A1:BL58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14579,7 +14615,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Evaluación</t>
+          <t>Prevención</t>
         </is>
       </c>
       <c r="H29" s="34">
@@ -17541,7 +17577,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Personas × días hábiles × horas</t>
+          <t>Personas × días hábiles × HH efectivas por día</t>
         </is>
       </c>
       <c r="H41" s="34">
@@ -18092,6 +18128,17 @@
       </c>
       <c r="F57" s="35">
         <f>SUMPRODUCT(--(H42:BK42&gt;0),--(H38:BK38&lt;=200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Comprobación capacidad de evaluadores = 2.150,4 HH/mes (16 × 21 × 6,4)</t>
+        </is>
+      </c>
+      <c r="F58" s="35">
+        <f>IF(ROUND(P42,1)=2150.4,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
@@ -18182,7 +18229,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1 = la prueba ocurre en el mes. Columnas rojas = congelamiento (1–25 sep. y diciembre, Caso RT-10.05). «Toca PROD» = la prueba interviene producción.</t>
+          <t>1 = la prueba ocurre en el mes. Columnas rojas = congelamiento (1–25 sep. y diciembre, Caso RT-10.05). «Toca PROD» = la prueba interviene producción. Las pruebas de septiembre se ejecutan los días 26 a 30, fuera del congelamiento (SD9 §9.3.3), por lo que sólo diciembre cuenta como conflicto.</t>
         </is>
       </c>
     </row>
@@ -18922,7 +18969,7 @@
         <v/>
       </c>
       <c r="BI7" s="13">
-        <f>IF(C7="Sí",SUMPRODUCT((D7:BG7=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C7="Sí",SUMPRODUCT((D7:BG7=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19007,7 +19054,7 @@
         <v/>
       </c>
       <c r="BI8" s="13">
-        <f>IF(C8="Sí",SUMPRODUCT((D8:BG8=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C8="Sí",SUMPRODUCT((D8:BG8=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19094,7 +19141,7 @@
         <v/>
       </c>
       <c r="BI9" s="13">
-        <f>IF(C9="Sí",SUMPRODUCT((D9:BG9=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C9="Sí",SUMPRODUCT((D9:BG9=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19179,7 +19226,7 @@
         <v/>
       </c>
       <c r="BI10" s="13">
-        <f>IF(C10="Sí",SUMPRODUCT((D10:BG10=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C10="Sí",SUMPRODUCT((D10:BG10=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19272,7 +19319,7 @@
         <v/>
       </c>
       <c r="BI11" s="13">
-        <f>IF(C11="Sí",SUMPRODUCT((D11:BG11=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C11="Sí",SUMPRODUCT((D11:BG11=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19331,10 +19378,10 @@
       <c r="AF12" s="39" t="n"/>
       <c r="AG12" s="39" t="n"/>
       <c r="AH12" s="39" t="n"/>
-      <c r="AI12" s="39" t="n"/>
-      <c r="AJ12" s="39" t="n">
+      <c r="AI12" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="AJ12" s="39" t="n"/>
       <c r="AK12" s="39" t="n"/>
       <c r="AL12" s="39" t="n"/>
       <c r="AM12" s="39" t="n"/>
@@ -19347,10 +19394,10 @@
       <c r="AR12" s="39" t="n"/>
       <c r="AS12" s="39" t="n"/>
       <c r="AT12" s="39" t="n"/>
-      <c r="AU12" s="39" t="n"/>
-      <c r="AV12" s="39" t="n">
+      <c r="AU12" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="AV12" s="39" t="n"/>
       <c r="AW12" s="39" t="n"/>
       <c r="AX12" s="39" t="n"/>
       <c r="AY12" s="39" t="n"/>
@@ -19371,7 +19418,7 @@
         <v/>
       </c>
       <c r="BI12" s="13">
-        <f>IF(C12="Sí",SUMPRODUCT((D12:BG12=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C12="Sí",SUMPRODUCT((D12:BG12=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19399,7 +19446,9 @@
       <c r="I13" s="39" t="n"/>
       <c r="J13" s="39" t="n"/>
       <c r="K13" s="39" t="n"/>
-      <c r="L13" s="39" t="n"/>
+      <c r="L13" s="39" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" s="39" t="n">
         <v>1</v>
       </c>
@@ -19429,10 +19478,10 @@
       <c r="AG13" s="39" t="n"/>
       <c r="AH13" s="39" t="n"/>
       <c r="AI13" s="39" t="n"/>
-      <c r="AJ13" s="39" t="n"/>
-      <c r="AK13" s="39" t="n">
+      <c r="AJ13" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="AK13" s="39" t="n"/>
       <c r="AL13" s="39" t="n"/>
       <c r="AM13" s="39" t="n"/>
       <c r="AN13" s="39" t="n"/>
@@ -19445,10 +19494,10 @@
       <c r="AS13" s="39" t="n"/>
       <c r="AT13" s="39" t="n"/>
       <c r="AU13" s="39" t="n"/>
-      <c r="AV13" s="39" t="n"/>
-      <c r="AW13" s="39" t="n">
+      <c r="AV13" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="AW13" s="39" t="n"/>
       <c r="AX13" s="39" t="n"/>
       <c r="AY13" s="39" t="n"/>
       <c r="AZ13" s="39" t="n"/>
@@ -19468,7 +19517,7 @@
         <v/>
       </c>
       <c r="BI13" s="13">
-        <f>IF(C13="Sí",SUMPRODUCT((D13:BG13=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C13="Sí",SUMPRODUCT((D13:BG13=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19499,7 +19548,9 @@
       <c r="L14" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="39" t="n"/>
+      <c r="M14" s="39" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" s="39" t="n"/>
       <c r="O14" s="39" t="n"/>
       <c r="P14" s="39" t="n"/>
@@ -19559,7 +19610,7 @@
         <v/>
       </c>
       <c r="BI14" s="13">
-        <f>IF(C14="Sí",SUMPRODUCT((D14:BG14=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C14="Sí",SUMPRODUCT((D14:BG14=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19646,7 +19697,7 @@
         <v/>
       </c>
       <c r="BI15" s="13">
-        <f>IF(C15="Sí",SUMPRODUCT((D15:BG15=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C15="Sí",SUMPRODUCT((D15:BG15=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19733,7 +19784,7 @@
         <v/>
       </c>
       <c r="BI16" s="13">
-        <f>IF(C16="Sí",SUMPRODUCT((D16:BG16=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C16="Sí",SUMPRODUCT((D16:BG16=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19816,7 +19867,7 @@
         <v/>
       </c>
       <c r="BI17" s="13">
-        <f>IF(C17="Sí",SUMPRODUCT((D17:BG17=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C17="Sí",SUMPRODUCT((D17:BG17=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>
@@ -19969,7 +20020,7 @@
         <v/>
       </c>
       <c r="BI18" s="13">
-        <f>IF(C18="Sí",SUMPRODUCT((D18:BG18=1)*(D$5:BG$5="CONG")),0)</f>
+        <f>IF(C18="Sí",SUMPRODUCT((D18:BG18=1)*(D$5:BG$5="CONG")*(MONTH(D$4:BG$4)=12)),0)</f>
         <v/>
       </c>
     </row>

--- a/09_plan_calidad/Diagramas/LafroX-Calculos-SD9.xlsx
+++ b/09_plan_calidad/Diagramas/LafroX-Calculos-SD9.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Base" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISO25010" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metricas_Codigo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carga_Estres" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilidad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos_Prueba" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HH_Calidad" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aceptacion_T17" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COQ" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metricas_Proceso" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inconsistencias" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figuras" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Base" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ISO25010" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Metricas_Codigo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Carga_Estres" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Disponibilidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Casos_Prueba" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="HH_Calidad" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Calendario" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Aceptacion_T17" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="COQ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Metricas_Proceso" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Inconsistencias" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Figuras" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>242</v>
+        <v>337</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
@@ -8060,11 +8060,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Comprobación: total = 1.297 casos, 1.038 automatizados y 259 manuales (SD9 §9.2.3; Anexo 9.C.1)</t>
+          <t>Comprobación: total = 1.305 casos, 1.044 automatizados y 261 manuales (SD9 §9.2.3; Anexo 9.C.1)</t>
         </is>
       </c>
       <c r="D26" s="3">
-        <f>IF(AND(D11=1297,D20=1038,D23=259),"OK","REVISAR")</f>
+        <f>IF(AND(D11=1305,D20=1044,D23=261),"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
